--- a/output/pdf_financials_xlsx/FWM.xlsx
+++ b/output/pdf_financials_xlsx/FWM.xlsx
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.163831</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.186867</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.187608</v>
       </c>
     </row>
     <row r="93">
@@ -3174,7 +3174,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3663,7 +3667,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.163831</v>
       </c>

--- a/output/pdf_financials_xlsx/FWM.xlsx
+++ b/output/pdf_financials_xlsx/FWM.xlsx
@@ -580,10 +580,10 @@
         <v>0.186836</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.157172</v>
+        <v>0.319151</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.157006</v>
+        <v>0.246106</v>
       </c>
     </row>
     <row r="11">
@@ -596,10 +596,10 @@
         <v>-0.186836</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.157172</v>
+        <v>-0.319151</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.157006</v>
+        <v>-0.246106</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00047</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000461</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000501</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.364339</v>
+        <v>-0.364809</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.2548</v>
+        <v>-0.255261</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.245605</v>
+        <v>-0.246106</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.363589</v>
+        <v>-0.364059</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.2548</v>
+        <v>-0.255261</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.245605</v>
+        <v>-0.246106</v>
       </c>
     </row>
     <row r="30">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0008630000000000001</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0008630000000000001</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -4926,7 +4926,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>-0.0008630000000000001</v>
       </c>
@@ -5771,7 +5775,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5780,10 +5784,10 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-0.319151</v>
+        <v>0.319151</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.246106</v>
+        <v>0.246106</v>
       </c>
     </row>
     <row r="99">
@@ -5835,7 +5839,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6717,7 +6721,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">

--- a/output/pdf_financials_xlsx/FWM.xlsx
+++ b/output/pdf_financials_xlsx/FWM.xlsx
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.008182999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -3857,7 +3857,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -4216,7 +4220,11 @@
           <t>Net proceeds from private placement</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -4600,7 +4608,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>1.1e-05</v>
       </c>
@@ -5023,7 +5035,11 @@
           <t>Net proceeds from private placement</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>0.36253</v>
       </c>
